--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H259"/>
+  <dimension ref="A1:H260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5512,6 +5512,25 @@
         <v>102</v>
       </c>
     </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>13</v>
+      </c>
+      <c r="C260" t="n">
+        <v>6</v>
+      </c>
+      <c r="D260" t="n">
+        <v>49</v>
+      </c>
+      <c r="E260" t="n">
+        <v>135</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H260"/>
+  <dimension ref="A1:H261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5531,6 +5531,25 @@
         <v>135</v>
       </c>
     </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>15</v>
+      </c>
+      <c r="C261" t="n">
+        <v>11</v>
+      </c>
+      <c r="D261" t="n">
+        <v>84</v>
+      </c>
+      <c r="E261" t="n">
+        <v>198</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H261"/>
+  <dimension ref="A1:H262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5550,6 +5550,25 @@
         <v>198</v>
       </c>
     </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>16</v>
+      </c>
+      <c r="C262" t="n">
+        <v>5</v>
+      </c>
+      <c r="D262" t="n">
+        <v>72</v>
+      </c>
+      <c r="E262" t="n">
+        <v>138</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H262"/>
+  <dimension ref="A1:H263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5569,6 +5569,25 @@
         <v>138</v>
       </c>
     </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>12</v>
+      </c>
+      <c r="C263" t="n">
+        <v>3</v>
+      </c>
+      <c r="D263" t="n">
+        <v>57</v>
+      </c>
+      <c r="E263" t="n">
+        <v>132</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H263"/>
+  <dimension ref="A1:H264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5588,6 +5588,25 @@
         <v>132</v>
       </c>
     </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>12</v>
+      </c>
+      <c r="C264" t="n">
+        <v>3</v>
+      </c>
+      <c r="D264" t="n">
+        <v>57</v>
+      </c>
+      <c r="E264" t="n">
+        <v>113</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H264"/>
+  <dimension ref="A1:H265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5607,6 +5607,25 @@
         <v>113</v>
       </c>
     </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>11</v>
+      </c>
+      <c r="C265" t="n">
+        <v>5</v>
+      </c>
+      <c r="D265" t="n">
+        <v>60</v>
+      </c>
+      <c r="E265" t="n">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H265"/>
+  <dimension ref="A1:H266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5626,6 +5626,25 @@
         <v>106</v>
       </c>
     </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>11</v>
+      </c>
+      <c r="C266" t="n">
+        <v>4</v>
+      </c>
+      <c r="D266" t="n">
+        <v>58</v>
+      </c>
+      <c r="E266" t="n">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H266"/>
+  <dimension ref="A1:H267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5645,6 +5645,25 @@
         <v>123</v>
       </c>
     </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>14</v>
+      </c>
+      <c r="C267" t="n">
+        <v>7</v>
+      </c>
+      <c r="D267" t="n">
+        <v>69</v>
+      </c>
+      <c r="E267" t="n">
+        <v>138</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H267"/>
+  <dimension ref="A1:H268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5664,6 +5664,25 @@
         <v>138</v>
       </c>
     </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>15</v>
+      </c>
+      <c r="C268" t="n">
+        <v>9</v>
+      </c>
+      <c r="D268" t="n">
+        <v>96</v>
+      </c>
+      <c r="E268" t="n">
+        <v>201</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H268"/>
+  <dimension ref="A1:H269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5683,6 +5683,25 @@
         <v>201</v>
       </c>
     </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>16</v>
+      </c>
+      <c r="C269" t="n">
+        <v>4</v>
+      </c>
+      <c r="D269" t="n">
+        <v>69</v>
+      </c>
+      <c r="E269" t="n">
+        <v>126</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H269"/>
+  <dimension ref="A1:H270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5702,6 +5702,25 @@
         <v>126</v>
       </c>
     </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>13</v>
+      </c>
+      <c r="C270" t="n">
+        <v>6</v>
+      </c>
+      <c r="D270" t="n">
+        <v>73</v>
+      </c>
+      <c r="E270" t="n">
+        <v>113</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H270"/>
+  <dimension ref="A1:H271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5721,6 +5721,25 @@
         <v>113</v>
       </c>
     </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>13</v>
+      </c>
+      <c r="C271" t="n">
+        <v>4</v>
+      </c>
+      <c r="D271" t="n">
+        <v>69</v>
+      </c>
+      <c r="E271" t="n">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H271"/>
+  <dimension ref="A1:H272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5740,6 +5740,25 @@
         <v>102</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>12</v>
+      </c>
+      <c r="C272" t="n">
+        <v>4</v>
+      </c>
+      <c r="D272" t="n">
+        <v>67</v>
+      </c>
+      <c r="E272" t="n">
+        <v>89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H272"/>
+  <dimension ref="A1:H273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5759,6 +5759,25 @@
         <v>89</v>
       </c>
     </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>12</v>
+      </c>
+      <c r="C273" t="n">
+        <v>4</v>
+      </c>
+      <c r="D273" t="n">
+        <v>43</v>
+      </c>
+      <c r="E273" t="n">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H273"/>
+  <dimension ref="A1:H274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5778,6 +5778,25 @@
         <v>98</v>
       </c>
     </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>14</v>
+      </c>
+      <c r="C274" t="n">
+        <v>8</v>
+      </c>
+      <c r="D274" t="n">
+        <v>69</v>
+      </c>
+      <c r="E274" t="n">
+        <v>128</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H274"/>
+  <dimension ref="A1:H275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5797,6 +5797,25 @@
         <v>128</v>
       </c>
     </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>17</v>
+      </c>
+      <c r="C275" t="n">
+        <v>9</v>
+      </c>
+      <c r="D275" t="n">
+        <v>76</v>
+      </c>
+      <c r="E275" t="n">
+        <v>165</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H275"/>
+  <dimension ref="A1:H276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5816,6 +5816,25 @@
         <v>165</v>
       </c>
     </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>12</v>
+      </c>
+      <c r="C276" t="n">
+        <v>5</v>
+      </c>
+      <c r="D276" t="n">
+        <v>49</v>
+      </c>
+      <c r="E276" t="n">
+        <v>128</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H276"/>
+  <dimension ref="A1:H277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5835,6 +5835,25 @@
         <v>128</v>
       </c>
     </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>11</v>
+      </c>
+      <c r="C277" t="n">
+        <v>5</v>
+      </c>
+      <c r="D277" t="n">
+        <v>53</v>
+      </c>
+      <c r="E277" t="n">
+        <v>109</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H277"/>
+  <dimension ref="A1:H278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5854,6 +5854,25 @@
         <v>109</v>
       </c>
     </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>11</v>
+      </c>
+      <c r="C278" t="n">
+        <v>5</v>
+      </c>
+      <c r="D278" t="n">
+        <v>43</v>
+      </c>
+      <c r="E278" t="n">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H278"/>
+  <dimension ref="A1:H279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5873,6 +5873,25 @@
         <v>110</v>
       </c>
     </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>10</v>
+      </c>
+      <c r="C279" t="n">
+        <v>5</v>
+      </c>
+      <c r="D279" t="n">
+        <v>51</v>
+      </c>
+      <c r="E279" t="n">
+        <v>94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H279"/>
+  <dimension ref="A1:H280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5892,6 +5892,25 @@
         <v>94</v>
       </c>
     </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>10</v>
+      </c>
+      <c r="C280" t="n">
+        <v>5</v>
+      </c>
+      <c r="D280" t="n">
+        <v>34</v>
+      </c>
+      <c r="E280" t="n">
+        <v>111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H280"/>
+  <dimension ref="A1:H281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5911,6 +5911,25 @@
         <v>111</v>
       </c>
     </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>12</v>
+      </c>
+      <c r="C281" t="n">
+        <v>8</v>
+      </c>
+      <c r="D281" t="n">
+        <v>43</v>
+      </c>
+      <c r="E281" t="n">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H281"/>
+  <dimension ref="A1:H282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5930,6 +5930,25 @@
         <v>123</v>
       </c>
     </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>14</v>
+      </c>
+      <c r="C282" t="n">
+        <v>9</v>
+      </c>
+      <c r="D282" t="n">
+        <v>58</v>
+      </c>
+      <c r="E282" t="n">
+        <v>161</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H282"/>
+  <dimension ref="A1:H283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5949,6 +5949,25 @@
         <v>161</v>
       </c>
     </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>12</v>
+      </c>
+      <c r="C283" t="n">
+        <v>6</v>
+      </c>
+      <c r="D283" t="n">
+        <v>85</v>
+      </c>
+      <c r="E283" t="n">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H283"/>
+  <dimension ref="A1:H284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5968,6 +5968,25 @@
         <v>123</v>
       </c>
     </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>11</v>
+      </c>
+      <c r="C284" t="n">
+        <v>5</v>
+      </c>
+      <c r="D284" t="n">
+        <v>65</v>
+      </c>
+      <c r="E284" t="n">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H284"/>
+  <dimension ref="A1:H285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5987,6 +5987,25 @@
         <v>103</v>
       </c>
     </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>10</v>
+      </c>
+      <c r="C285" t="n">
+        <v>6</v>
+      </c>
+      <c r="D285" t="n">
+        <v>64</v>
+      </c>
+      <c r="E285" t="n">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H285"/>
+  <dimension ref="A1:H286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6006,6 +6006,25 @@
         <v>105</v>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>10</v>
+      </c>
+      <c r="C286" t="n">
+        <v>6</v>
+      </c>
+      <c r="D286" t="n">
+        <v>40</v>
+      </c>
+      <c r="E286" t="n">
+        <v>95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H286"/>
+  <dimension ref="A1:H287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6025,6 +6025,25 @@
         <v>95</v>
       </c>
     </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>12</v>
+      </c>
+      <c r="C287" t="n">
+        <v>5</v>
+      </c>
+      <c r="D287" t="n">
+        <v>37</v>
+      </c>
+      <c r="E287" t="n">
+        <v>88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H287"/>
+  <dimension ref="A1:H288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6044,6 +6044,25 @@
         <v>88</v>
       </c>
     </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>12</v>
+      </c>
+      <c r="C288" t="n">
+        <v>7</v>
+      </c>
+      <c r="D288" t="n">
+        <v>54</v>
+      </c>
+      <c r="E288" t="n">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H288"/>
+  <dimension ref="A1:H289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6063,6 +6063,25 @@
         <v>101</v>
       </c>
     </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>12</v>
+      </c>
+      <c r="C289" t="n">
+        <v>8</v>
+      </c>
+      <c r="D289" t="n">
+        <v>66</v>
+      </c>
+      <c r="E289" t="n">
+        <v>162</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H289"/>
+  <dimension ref="A1:H290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6082,6 +6082,25 @@
         <v>162</v>
       </c>
     </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>12</v>
+      </c>
+      <c r="C290" t="n">
+        <v>6</v>
+      </c>
+      <c r="D290" t="n">
+        <v>66</v>
+      </c>
+      <c r="E290" t="n">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H290"/>
+  <dimension ref="A1:H291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6101,6 +6101,25 @@
         <v>123</v>
       </c>
     </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>10</v>
+      </c>
+      <c r="C291" t="n">
+        <v>5</v>
+      </c>
+      <c r="D291" t="n">
+        <v>42</v>
+      </c>
+      <c r="E291" t="n">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H291"/>
+  <dimension ref="A1:H292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6120,6 +6120,25 @@
         <v>102</v>
       </c>
     </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>10</v>
+      </c>
+      <c r="C292" t="n">
+        <v>5</v>
+      </c>
+      <c r="D292" t="n">
+        <v>44</v>
+      </c>
+      <c r="E292" t="n">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H292"/>
+  <dimension ref="A1:H293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6139,6 +6139,25 @@
         <v>97</v>
       </c>
     </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>9</v>
+      </c>
+      <c r="C293" t="n">
+        <v>6</v>
+      </c>
+      <c r="D293" t="n">
+        <v>55</v>
+      </c>
+      <c r="E293" t="n">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H293"/>
+  <dimension ref="A1:H294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6158,6 +6158,25 @@
         <v>86</v>
       </c>
     </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>10</v>
+      </c>
+      <c r="C294" t="n">
+        <v>4</v>
+      </c>
+      <c r="D294" t="n">
+        <v>58</v>
+      </c>
+      <c r="E294" t="n">
+        <v>93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H294"/>
+  <dimension ref="A1:H295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6177,6 +6177,25 @@
         <v>93</v>
       </c>
     </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>10</v>
+      </c>
+      <c r="C295" t="n">
+        <v>4</v>
+      </c>
+      <c r="D295" t="n">
+        <v>64</v>
+      </c>
+      <c r="E295" t="n">
+        <v>129</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H295"/>
+  <dimension ref="A1:H296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6196,6 +6196,25 @@
         <v>129</v>
       </c>
     </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>11</v>
+      </c>
+      <c r="C296" t="n">
+        <v>7</v>
+      </c>
+      <c r="D296" t="n">
+        <v>72</v>
+      </c>
+      <c r="E296" t="n">
+        <v>172</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H296"/>
+  <dimension ref="A1:H297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6215,6 +6215,25 @@
         <v>172</v>
       </c>
     </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>12</v>
+      </c>
+      <c r="C297" t="n">
+        <v>5</v>
+      </c>
+      <c r="D297" t="n">
+        <v>81</v>
+      </c>
+      <c r="E297" t="n">
+        <v>112</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H297"/>
+  <dimension ref="A1:H298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6234,6 +6234,25 @@
         <v>112</v>
       </c>
     </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>10</v>
+      </c>
+      <c r="C298" t="n">
+        <v>4</v>
+      </c>
+      <c r="D298" t="n">
+        <v>52</v>
+      </c>
+      <c r="E298" t="n">
+        <v>118</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H298"/>
+  <dimension ref="A1:H299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6253,6 +6253,25 @@
         <v>118</v>
       </c>
     </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>9</v>
+      </c>
+      <c r="C299" t="n">
+        <v>5</v>
+      </c>
+      <c r="D299" t="n">
+        <v>42</v>
+      </c>
+      <c r="E299" t="n">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H299"/>
+  <dimension ref="A1:H300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6272,6 +6272,25 @@
         <v>104</v>
       </c>
     </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>8</v>
+      </c>
+      <c r="C300" t="n">
+        <v>5</v>
+      </c>
+      <c r="D300" t="n">
+        <v>35</v>
+      </c>
+      <c r="E300" t="n">
+        <v>114</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H300"/>
+  <dimension ref="A1:H303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6291,6 +6291,63 @@
         <v>114</v>
       </c>
     </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>8</v>
+      </c>
+      <c r="C301" t="n">
+        <v>5</v>
+      </c>
+      <c r="D301" t="n">
+        <v>28</v>
+      </c>
+      <c r="E301" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>11</v>
+      </c>
+      <c r="C302" t="n">
+        <v>5</v>
+      </c>
+      <c r="D302" t="n">
+        <v>42</v>
+      </c>
+      <c r="E302" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>10</v>
+      </c>
+      <c r="C303" t="n">
+        <v>5</v>
+      </c>
+      <c r="D303" t="n">
+        <v>51</v>
+      </c>
+      <c r="E303" t="n">
+        <v>180</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H303"/>
+  <dimension ref="A1:H304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6348,6 +6348,25 @@
         <v>180</v>
       </c>
     </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>9</v>
+      </c>
+      <c r="C304" t="n">
+        <v>5</v>
+      </c>
+      <c r="D304" t="n">
+        <v>59</v>
+      </c>
+      <c r="E304" t="n">
+        <v>111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H304"/>
+  <dimension ref="A1:H305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6367,6 +6367,25 @@
         <v>111</v>
       </c>
     </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>9</v>
+      </c>
+      <c r="C305" t="n">
+        <v>5</v>
+      </c>
+      <c r="D305" t="n">
+        <v>46</v>
+      </c>
+      <c r="E305" t="n">
+        <v>112</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H305"/>
+  <dimension ref="A1:H306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6386,6 +6386,25 @@
         <v>112</v>
       </c>
     </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>9</v>
+      </c>
+      <c r="C306" t="n">
+        <v>4</v>
+      </c>
+      <c r="D306" t="n">
+        <v>46</v>
+      </c>
+      <c r="E306" t="n">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H306"/>
+  <dimension ref="A1:H307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6405,6 +6405,25 @@
         <v>92</v>
       </c>
     </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>9</v>
+      </c>
+      <c r="C307" t="n">
+        <v>4</v>
+      </c>
+      <c r="D307" t="n">
+        <v>45</v>
+      </c>
+      <c r="E307" t="n">
+        <v>99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plejd_sensortower_rankings.xlsx
+++ b/data/plejd_sensortower_rankings.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H307"/>
+  <dimension ref="A1:H308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6424,6 +6424,25 @@
         <v>99</v>
       </c>
     </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>8</v>
+      </c>
+      <c r="C308" t="n">
+        <v>6</v>
+      </c>
+      <c r="D308" t="n">
+        <v>28</v>
+      </c>
+      <c r="E308" t="n">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
